--- a/astro-site/public/dl/pastry-shop-checklist-templates/11-cake-order-form-order-log.xlsx
+++ b/astro-site/public/dl/pastry-shop-checklist-templates/11-cake-order-form-order-log.xlsx
@@ -915,7 +915,7 @@
     <row r="17">
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Privacy (kit guideline, not legal advice): this form collects personal data and HEALTH data (allergies). Before printing it, write the business name and contact in the green cell at the bottom. Collect only what you need. The allergy consent box is separate from the marketing one and neither may be pre-checked. Keep the forms locked up, not in view at the counter, and shred them one month after pickup, except what you need for taxes. Check your state's privacy law.</t>
+          <t>Privacy (kit guideline, not legal advice): this form collects personal data and HEALTH data (allergies). Before printing it, write the business name and contact in the green cell at the bottom. Collect only what you need. The allergy consent box is separate from the marketing one and neither may be pre-checked. Keep the forms locked up, not in view at the counter, for as long as your insurer or attorney advises (the form is your record if an allergy claim ever comes up), then shred them. Check your state's privacy law.</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
     <row r="23" ht="44" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>Check what the customer declares. Look up each item's spec sheet before accepting the order (→ 12 Bakery Allergen Chart · sheet "Allergen Chart"). The first 9 are the major US allergens (FALCPA + FASTER Act); the rest are gluten for celiacs and the UK ones.</t>
+          <t>Check what the customer declares. Look up each item's spec sheet before accepting the order (→ 12 Bakery Allergen Chart · sheet "Allergen Chart"). The first 9 are the major US allergens (FALCPA + FASTER Act); the rest are gluten for celiacs, sulfites and the UK ones.</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
     <row r="46" ht="37.3" customHeight="1">
       <c r="A46" s="16" t="inlineStr">
         <is>
-          <t>Privacy notice. Who: the business named on this form. Why: to take, prepare, deliver and invoice this order. Allergies: used only to prepare the order safely, with the consent given above. Other people's information: shared with their permission. How long: destroyed one month after pickup, except what taxes require. We do not sell or share your information. Questions: ask at the counter or write to ______________________________.</t>
+          <t>Privacy notice. Who: the business named on this form. Why: to take, prepare, deliver and invoice this order. Allergies: used only to prepare the order safely, with the consent given above. Other people's information: shared with their permission. How long: kept only as long as needed for the order, taxes and possible claims, then destroyed. We do not sell or share your information. Questions: ask at the counter or write to ______________________________.</t>
         </is>
       </c>
       <c r="B46" s="38" t="n"/>
@@ -3130,7 +3130,7 @@
     <row r="17" ht="26" customHeight="1">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>7:30 PM</t>
         </is>
       </c>
       <c r="B17" s="13" t="n"/>
